--- a/詳細設計図/タスク登録機能_詳細設計図.xlsx
+++ b/詳細設計図/タスク登録機能_詳細設計図.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" state="visible" r:id="rId3"/>
@@ -315,11 +315,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m\月d\日"/>
-    <numFmt numFmtId="166" formatCode="m\月d\日"/>
-    <numFmt numFmtId="167" formatCode="[$-411]h:mm"/>
+    <numFmt numFmtId="166" formatCode="[$-411]h:mm"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -657,7 +656,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -794,15 +793,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1030,16 +1025,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>964800</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>104760</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>83880</xdr:rowOff>
+      <xdr:rowOff>85680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>424800</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>26640</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1086840</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>61560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1052,8 +1047,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2052720" y="998280"/>
-          <a:ext cx="5346360" cy="4476600"/>
+          <a:off x="104760" y="1000080"/>
+          <a:ext cx="9133560" cy="5805360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5138,7 +5133,7 @@
         <v>13</v>
       </c>
       <c r="G2" s="13"/>
-      <c r="H2" s="34" t="n">
+      <c r="H2" s="23" t="n">
         <v>45706</v>
       </c>
       <c r="I2" s="13" t="s">
@@ -5154,8 +5149,8 @@
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
       <c r="J3" s="14"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5166,370 +5161,469 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
       <c r="J4" s="14"/>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="35"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="35"/>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
+      <c r="A6" s="34"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="35"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="35"/>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
+      <c r="A8" s="34"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="35"/>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35"/>
+      <c r="A9" s="34"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="35"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
+      <c r="A10" s="34"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="35"/>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="35"/>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="35"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="35"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="35"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="34"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="35"/>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="35"/>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="35"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="35"/>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
+      <c r="A18" s="34"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="34"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="35"/>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
+      <c r="A19" s="34"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="35"/>
-      <c r="B20" s="35"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
+      <c r="A20" s="34"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="34"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="35"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="35"/>
+      <c r="A21" s="34"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="35"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
+      <c r="A22" s="34"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="35"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
+      <c r="A23" s="34"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="35"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="35"/>
+      <c r="A24" s="34"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="34"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="35"/>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="35"/>
+      <c r="A25" s="34"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="35"/>
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="35"/>
+      <c r="A26" s="34"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="34"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="35"/>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="35"/>
+      <c r="A27" s="34"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="34"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="35"/>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="35"/>
+      <c r="A28" s="34"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="35"/>
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="35"/>
-      <c r="J29" s="35"/>
+      <c r="A29" s="34"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="34"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="35"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="35"/>
-      <c r="J30" s="35"/>
+      <c r="A30" s="34"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="34"/>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="35"/>
-      <c r="B31" s="35"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="35"/>
+      <c r="A31" s="34"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="34"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="35"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="35"/>
-      <c r="J32" s="35"/>
+      <c r="A32" s="34"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="34"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="35"/>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="35"/>
-      <c r="J33" s="35"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="A33" s="34"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="34"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="34"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="34"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="34"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="34"/>
+      <c r="J35" s="34"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="34"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="34"/>
+      <c r="I36" s="34"/>
+      <c r="J36" s="34"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="34"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="34"/>
+      <c r="I37" s="34"/>
+      <c r="J37" s="34"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="34"/>
+      <c r="B38" s="34"/>
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="34"/>
+      <c r="G38" s="34"/>
+      <c r="H38" s="34"/>
+      <c r="I38" s="34"/>
+      <c r="J38" s="34"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="34"/>
+      <c r="B39" s="34"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="34"/>
+      <c r="I39" s="34"/>
+      <c r="J39" s="34"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="34"/>
+      <c r="B40" s="34"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="34"/>
+      <c r="H40" s="34"/>
+      <c r="I40" s="34"/>
+      <c r="J40" s="34"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="34"/>
+      <c r="B41" s="34"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="34"/>
+      <c r="I41" s="34"/>
+      <c r="J41" s="34"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="34"/>
+      <c r="B42" s="34"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="34"/>
+      <c r="H42" s="34"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="34"/>
+    </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J44" s="36"/>
+      <c r="J44" s="35"/>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -6497,7 +6591,7 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:J33"/>
+    <mergeCell ref="A5:J42"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.708333333333333" right="0.708333333333333" top="0.747916666666667" bottom="0.747916666666667" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6524,11 +6618,11 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
       <c r="D1" s="10" t="s">
         <v>6</v>
       </c>
@@ -6548,9 +6642,9 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="37"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
+      <c r="A2" s="36"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
       <c r="D2" s="13" t="s">
         <v>12</v>
       </c>
@@ -6559,288 +6653,288 @@
         <v>13</v>
       </c>
       <c r="G2" s="13"/>
-      <c r="H2" s="34" t="n">
+      <c r="H2" s="23" t="n">
         <v>45706</v>
       </c>
       <c r="I2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="38"/>
+      <c r="J2" s="37"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="37"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
+      <c r="A3" s="36"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="38"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="37"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="38"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="37"/>
     </row>
     <row r="5" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="40" t="s">
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
     </row>
     <row r="6" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
     </row>
     <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="42"/>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
+      <c r="A7" s="41"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
     </row>
     <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="42"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
+      <c r="A8" s="41"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
     </row>
     <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="42"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="42"/>
+      <c r="A9" s="41"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="42"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
+      <c r="A10" s="41"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="42"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42"/>
+      <c r="A11" s="41"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="42"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
+      <c r="A12" s="41"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="42"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="42"/>
+      <c r="A13" s="41"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="43" t="s">
+      <c r="A15" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="45" t="s">
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="J15" s="46" t="s">
+      <c r="J15" s="45" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="45" t="s">
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="45" t="s">
+      <c r="E16" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="45" t="s">
+      <c r="F16" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="G16" s="45" t="s">
+      <c r="G16" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="H16" s="47" t="s">
+      <c r="H16" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="47"/>
-      <c r="J16" s="47"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="46"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="48"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
+      <c r="A17" s="47"/>
+      <c r="B17" s="47"/>
+      <c r="C17" s="47"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
       <c r="H17" s="27"/>
       <c r="I17" s="27"/>
       <c r="J17" s="27"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
-      <c r="C18" s="48"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
+      <c r="C18" s="47"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
       <c r="H18" s="27"/>
       <c r="I18" s="27"/>
       <c r="J18" s="27"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
+      <c r="A19" s="47"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
       <c r="H19" s="27"/>
       <c r="I19" s="27"/>
       <c r="J19" s="27"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="48"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="48"/>
+      <c r="A20" s="47"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="47"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
       <c r="H20" s="27"/>
       <c r="I20" s="27"/>
       <c r="J20" s="27"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="48"/>
-      <c r="B21" s="48"/>
-      <c r="C21" s="48"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="47"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
       <c r="H21" s="27"/>
       <c r="I21" s="27"/>
       <c r="J21" s="27"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="48"/>
-      <c r="B22" s="48"/>
-      <c r="C22" s="48"/>
+      <c r="A22" s="47"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
       <c r="H22" s="27"/>
       <c r="I22" s="27"/>
       <c r="J22" s="27"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="49"/>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
+      <c r="A23" s="48"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="48"/>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="50"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
       <c r="H23" s="33"/>
       <c r="I23" s="33"/>
       <c r="J23" s="33"/>
@@ -7980,14 +8074,14 @@
       <c r="T4" s="14"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
       <c r="G5" s="25" t="s">
         <v>50</v>
       </c>
@@ -8006,14 +8100,14 @@
       <c r="T5" s="25"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
       <c r="G6" s="27" t="s">
         <v>5</v>
       </c>
@@ -8032,14 +8126,14 @@
       <c r="T6" s="27"/>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
       <c r="G7" s="27" t="s">
         <v>53</v>
       </c>
@@ -8080,156 +8174,156 @@
       <c r="T8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="51"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="53" t="s">
+      <c r="A9" s="50"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54" t="s">
+      <c r="D9" s="53"/>
+      <c r="E9" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="54"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="54"/>
-      <c r="K9" s="55"/>
-      <c r="L9" s="52"/>
-      <c r="M9" s="52"/>
-      <c r="N9" s="52"/>
-      <c r="O9" s="52"/>
-      <c r="P9" s="52"/>
-      <c r="Q9" s="52"/>
-      <c r="R9" s="52"/>
-      <c r="S9" s="52"/>
-      <c r="T9" s="56"/>
-      <c r="U9" s="52"/>
-      <c r="V9" s="52"/>
-      <c r="W9" s="52"/>
-      <c r="X9" s="52"/>
-      <c r="Y9" s="52"/>
-      <c r="Z9" s="52"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="53"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="51"/>
+      <c r="M9" s="51"/>
+      <c r="N9" s="51"/>
+      <c r="O9" s="51"/>
+      <c r="P9" s="51"/>
+      <c r="Q9" s="51"/>
+      <c r="R9" s="51"/>
+      <c r="S9" s="51"/>
+      <c r="T9" s="55"/>
+      <c r="U9" s="51"/>
+      <c r="V9" s="51"/>
+      <c r="W9" s="51"/>
+      <c r="X9" s="51"/>
+      <c r="Y9" s="51"/>
+      <c r="Z9" s="51"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="51"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52" t="s">
+      <c r="A10" s="50"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="52"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
-      <c r="K10" s="58"/>
-      <c r="L10" s="52"/>
-      <c r="M10" s="52"/>
-      <c r="N10" s="52"/>
-      <c r="O10" s="52"/>
-      <c r="P10" s="52"/>
-      <c r="Q10" s="52"/>
-      <c r="R10" s="52"/>
-      <c r="S10" s="52"/>
-      <c r="T10" s="56"/>
-      <c r="U10" s="52"/>
-      <c r="V10" s="52"/>
-      <c r="W10" s="52"/>
-      <c r="X10" s="52"/>
-      <c r="Y10" s="52"/>
-      <c r="Z10" s="52"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="51"/>
+      <c r="N10" s="51"/>
+      <c r="O10" s="51"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="51"/>
+      <c r="R10" s="51"/>
+      <c r="S10" s="51"/>
+      <c r="T10" s="55"/>
+      <c r="U10" s="51"/>
+      <c r="V10" s="51"/>
+      <c r="W10" s="51"/>
+      <c r="X10" s="51"/>
+      <c r="Y10" s="51"/>
+      <c r="Z10" s="51"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="51"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52" t="s">
+      <c r="A11" s="50"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="52"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="52"/>
-      <c r="K11" s="58"/>
-      <c r="L11" s="52"/>
-      <c r="M11" s="52"/>
-      <c r="N11" s="52"/>
-      <c r="O11" s="52"/>
-      <c r="P11" s="52"/>
-      <c r="Q11" s="52"/>
-      <c r="R11" s="52"/>
-      <c r="S11" s="52"/>
-      <c r="T11" s="56"/>
-      <c r="U11" s="52"/>
-      <c r="V11" s="52"/>
-      <c r="W11" s="52"/>
-      <c r="X11" s="52"/>
-      <c r="Y11" s="52"/>
-      <c r="Z11" s="52"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="51"/>
+      <c r="O11" s="51"/>
+      <c r="P11" s="51"/>
+      <c r="Q11" s="51"/>
+      <c r="R11" s="51"/>
+      <c r="S11" s="51"/>
+      <c r="T11" s="55"/>
+      <c r="U11" s="51"/>
+      <c r="V11" s="51"/>
+      <c r="W11" s="51"/>
+      <c r="X11" s="51"/>
+      <c r="Y11" s="51"/>
+      <c r="Z11" s="51"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52" t="s">
+      <c r="A12" s="50"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="52"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="52"/>
-      <c r="K12" s="58"/>
-      <c r="L12" s="52"/>
-      <c r="M12" s="52"/>
-      <c r="N12" s="52"/>
-      <c r="O12" s="52"/>
-      <c r="P12" s="52"/>
-      <c r="Q12" s="52"/>
-      <c r="R12" s="52"/>
-      <c r="S12" s="52"/>
-      <c r="T12" s="56"/>
-      <c r="U12" s="52"/>
-      <c r="V12" s="52"/>
-      <c r="W12" s="52"/>
-      <c r="X12" s="52"/>
-      <c r="Y12" s="52"/>
-      <c r="Z12" s="52"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="57"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="51"/>
+      <c r="O12" s="51"/>
+      <c r="P12" s="51"/>
+      <c r="Q12" s="51"/>
+      <c r="R12" s="51"/>
+      <c r="S12" s="51"/>
+      <c r="T12" s="55"/>
+      <c r="U12" s="51"/>
+      <c r="V12" s="51"/>
+      <c r="W12" s="51"/>
+      <c r="X12" s="51"/>
+      <c r="Y12" s="51"/>
+      <c r="Z12" s="51"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60" t="s">
+      <c r="A13" s="50"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="F13" s="60"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="60"/>
-      <c r="K13" s="61"/>
-      <c r="L13" s="52"/>
-      <c r="M13" s="52"/>
-      <c r="N13" s="52"/>
-      <c r="O13" s="52"/>
-      <c r="P13" s="52"/>
-      <c r="Q13" s="52"/>
-      <c r="R13" s="52"/>
-      <c r="S13" s="52"/>
-      <c r="T13" s="56"/>
-      <c r="U13" s="52"/>
-      <c r="V13" s="52"/>
-      <c r="W13" s="52"/>
-      <c r="X13" s="52"/>
-      <c r="Y13" s="52"/>
-      <c r="Z13" s="52"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="60"/>
+      <c r="L13" s="51"/>
+      <c r="M13" s="51"/>
+      <c r="N13" s="51"/>
+      <c r="O13" s="51"/>
+      <c r="P13" s="51"/>
+      <c r="Q13" s="51"/>
+      <c r="R13" s="51"/>
+      <c r="S13" s="51"/>
+      <c r="T13" s="55"/>
+      <c r="U13" s="51"/>
+      <c r="V13" s="51"/>
+      <c r="W13" s="51"/>
+      <c r="X13" s="51"/>
+      <c r="Y13" s="51"/>
+      <c r="Z13" s="51"/>
     </row>
     <row r="14" customFormat="false" ht="8.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15"/>
@@ -8254,522 +8348,522 @@
       <c r="T14" s="17"/>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="43" t="s">
+      <c r="A15" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="62" t="s">
+      <c r="B15" s="42"/>
+      <c r="C15" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="62"/>
-      <c r="E15" s="45" t="s">
+      <c r="D15" s="61"/>
+      <c r="E15" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45" t="s">
+      <c r="F15" s="44"/>
+      <c r="G15" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45" t="s">
+      <c r="H15" s="44"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="K15" s="45"/>
-      <c r="L15" s="45" t="s">
+      <c r="K15" s="44"/>
+      <c r="L15" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="M15" s="45"/>
-      <c r="N15" s="45"/>
-      <c r="O15" s="45" t="s">
+      <c r="M15" s="44"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="P15" s="45"/>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="45" t="s">
+      <c r="P15" s="44"/>
+      <c r="Q15" s="44"/>
+      <c r="R15" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="S15" s="45" t="s">
+      <c r="S15" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="T15" s="47" t="s">
+      <c r="T15" s="46" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="63" t="n">
+      <c r="A16" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="63"/>
-      <c r="C16" s="64" t="s">
+      <c r="B16" s="62"/>
+      <c r="C16" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="D16" s="64"/>
-      <c r="E16" s="64" t="s">
+      <c r="D16" s="63"/>
+      <c r="E16" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="F16" s="64"/>
-      <c r="G16" s="65" t="s">
+      <c r="F16" s="63"/>
+      <c r="G16" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="H16" s="65"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="65" t="s">
+      <c r="H16" s="64"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="K16" s="65"/>
-      <c r="L16" s="66" t="s">
+      <c r="K16" s="64"/>
+      <c r="L16" s="65" t="s">
         <v>73</v>
       </c>
-      <c r="M16" s="66"/>
-      <c r="N16" s="66"/>
-      <c r="O16" s="66" t="s">
+      <c r="M16" s="65"/>
+      <c r="N16" s="65"/>
+      <c r="O16" s="65" t="s">
         <v>74</v>
       </c>
-      <c r="P16" s="66"/>
-      <c r="Q16" s="66"/>
-      <c r="R16" s="66"/>
-      <c r="S16" s="66"/>
-      <c r="T16" s="67"/>
-      <c r="U16" s="68"/>
-      <c r="V16" s="68"/>
-      <c r="W16" s="68"/>
-      <c r="X16" s="68"/>
-      <c r="Y16" s="68"/>
-      <c r="Z16" s="68"/>
+      <c r="P16" s="65"/>
+      <c r="Q16" s="65"/>
+      <c r="R16" s="65"/>
+      <c r="S16" s="65"/>
+      <c r="T16" s="66"/>
+      <c r="U16" s="67"/>
+      <c r="V16" s="67"/>
+      <c r="W16" s="67"/>
+      <c r="X16" s="67"/>
+      <c r="Y16" s="67"/>
+      <c r="Z16" s="67"/>
     </row>
     <row r="17" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="63" t="n">
+      <c r="A17" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="63"/>
-      <c r="C17" s="64" t="s">
+      <c r="B17" s="62"/>
+      <c r="C17" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64" t="s">
+      <c r="D17" s="63"/>
+      <c r="E17" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="F17" s="64"/>
-      <c r="G17" s="65" t="s">
+      <c r="F17" s="63"/>
+      <c r="G17" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="H17" s="65"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="65" t="s">
+      <c r="H17" s="64"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="K17" s="65"/>
-      <c r="L17" s="66" t="s">
+      <c r="K17" s="64"/>
+      <c r="L17" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="M17" s="66"/>
-      <c r="N17" s="66"/>
-      <c r="O17" s="66" t="s">
+      <c r="M17" s="65"/>
+      <c r="N17" s="65"/>
+      <c r="O17" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="P17" s="66"/>
-      <c r="Q17" s="66"/>
-      <c r="R17" s="66"/>
-      <c r="S17" s="66"/>
-      <c r="T17" s="67"/>
-      <c r="U17" s="68"/>
-      <c r="V17" s="68"/>
-      <c r="W17" s="68"/>
-      <c r="X17" s="68"/>
-      <c r="Y17" s="68"/>
-      <c r="Z17" s="68"/>
+      <c r="P17" s="65"/>
+      <c r="Q17" s="65"/>
+      <c r="R17" s="65"/>
+      <c r="S17" s="65"/>
+      <c r="T17" s="66"/>
+      <c r="U17" s="67"/>
+      <c r="V17" s="67"/>
+      <c r="W17" s="67"/>
+      <c r="X17" s="67"/>
+      <c r="Y17" s="67"/>
+      <c r="Z17" s="67"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="63"/>
-      <c r="B18" s="63"/>
-      <c r="C18" s="64"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64"/>
-      <c r="F18" s="64"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="65"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="65"/>
-      <c r="K18" s="65"/>
-      <c r="L18" s="66"/>
-      <c r="M18" s="66"/>
-      <c r="N18" s="66"/>
-      <c r="O18" s="66"/>
-      <c r="P18" s="66"/>
-      <c r="Q18" s="66"/>
-      <c r="R18" s="66"/>
-      <c r="S18" s="66"/>
-      <c r="T18" s="67"/>
-      <c r="U18" s="68"/>
-      <c r="V18" s="68"/>
-      <c r="W18" s="68"/>
-      <c r="X18" s="68"/>
-      <c r="Y18" s="68"/>
-      <c r="Z18" s="68"/>
+      <c r="A18" s="62"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="64"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="65"/>
+      <c r="M18" s="65"/>
+      <c r="N18" s="65"/>
+      <c r="O18" s="65"/>
+      <c r="P18" s="65"/>
+      <c r="Q18" s="65"/>
+      <c r="R18" s="65"/>
+      <c r="S18" s="65"/>
+      <c r="T18" s="66"/>
+      <c r="U18" s="67"/>
+      <c r="V18" s="67"/>
+      <c r="W18" s="67"/>
+      <c r="X18" s="67"/>
+      <c r="Y18" s="67"/>
+      <c r="Z18" s="67"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="63"/>
-      <c r="B19" s="63"/>
-      <c r="C19" s="64"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="64"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="65"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="65"/>
-      <c r="K19" s="65"/>
-      <c r="L19" s="66"/>
-      <c r="M19" s="66"/>
-      <c r="N19" s="66"/>
-      <c r="O19" s="66"/>
-      <c r="P19" s="66"/>
-      <c r="Q19" s="66"/>
-      <c r="R19" s="66"/>
-      <c r="S19" s="66"/>
-      <c r="T19" s="67"/>
-      <c r="U19" s="68"/>
-      <c r="V19" s="68"/>
-      <c r="W19" s="68"/>
-      <c r="X19" s="68"/>
-      <c r="Y19" s="68"/>
-      <c r="Z19" s="68"/>
+      <c r="A19" s="62"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="64"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="64"/>
+      <c r="K19" s="64"/>
+      <c r="L19" s="65"/>
+      <c r="M19" s="65"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="65"/>
+      <c r="P19" s="65"/>
+      <c r="Q19" s="65"/>
+      <c r="R19" s="65"/>
+      <c r="S19" s="65"/>
+      <c r="T19" s="66"/>
+      <c r="U19" s="67"/>
+      <c r="V19" s="67"/>
+      <c r="W19" s="67"/>
+      <c r="X19" s="67"/>
+      <c r="Y19" s="67"/>
+      <c r="Z19" s="67"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="63"/>
-      <c r="B20" s="63"/>
-      <c r="C20" s="64"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="64"/>
-      <c r="G20" s="65"/>
-      <c r="H20" s="65"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="65"/>
-      <c r="K20" s="65"/>
-      <c r="L20" s="66"/>
-      <c r="M20" s="66"/>
-      <c r="N20" s="66"/>
-      <c r="O20" s="66"/>
-      <c r="P20" s="66"/>
-      <c r="Q20" s="66"/>
-      <c r="R20" s="66"/>
-      <c r="S20" s="66"/>
-      <c r="T20" s="67"/>
-      <c r="U20" s="68"/>
-      <c r="V20" s="68"/>
-      <c r="W20" s="68"/>
-      <c r="X20" s="68"/>
-      <c r="Y20" s="68"/>
-      <c r="Z20" s="68"/>
+      <c r="A20" s="62"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="63"/>
+      <c r="D20" s="63"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="64"/>
+      <c r="K20" s="64"/>
+      <c r="L20" s="65"/>
+      <c r="M20" s="65"/>
+      <c r="N20" s="65"/>
+      <c r="O20" s="65"/>
+      <c r="P20" s="65"/>
+      <c r="Q20" s="65"/>
+      <c r="R20" s="65"/>
+      <c r="S20" s="65"/>
+      <c r="T20" s="66"/>
+      <c r="U20" s="67"/>
+      <c r="V20" s="67"/>
+      <c r="W20" s="67"/>
+      <c r="X20" s="67"/>
+      <c r="Y20" s="67"/>
+      <c r="Z20" s="67"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="63"/>
-      <c r="B21" s="63"/>
-      <c r="C21" s="64"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="65"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="65"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="66"/>
-      <c r="M21" s="66"/>
-      <c r="N21" s="66"/>
-      <c r="O21" s="66"/>
-      <c r="P21" s="66"/>
-      <c r="Q21" s="66"/>
-      <c r="R21" s="66"/>
-      <c r="S21" s="66"/>
-      <c r="T21" s="67"/>
-      <c r="U21" s="68"/>
-      <c r="V21" s="68"/>
-      <c r="W21" s="68"/>
-      <c r="X21" s="68"/>
-      <c r="Y21" s="68"/>
-      <c r="Z21" s="68"/>
+      <c r="A21" s="62"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="63"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="63"/>
+      <c r="F21" s="63"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="64"/>
+      <c r="K21" s="64"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="65"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="65"/>
+      <c r="P21" s="65"/>
+      <c r="Q21" s="65"/>
+      <c r="R21" s="65"/>
+      <c r="S21" s="65"/>
+      <c r="T21" s="66"/>
+      <c r="U21" s="67"/>
+      <c r="V21" s="67"/>
+      <c r="W21" s="67"/>
+      <c r="X21" s="67"/>
+      <c r="Y21" s="67"/>
+      <c r="Z21" s="67"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="63"/>
-      <c r="B22" s="63"/>
-      <c r="C22" s="64"/>
-      <c r="D22" s="64"/>
-      <c r="E22" s="64"/>
-      <c r="F22" s="64"/>
-      <c r="G22" s="65"/>
-      <c r="H22" s="65"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="65"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="66"/>
-      <c r="M22" s="66"/>
-      <c r="N22" s="66"/>
-      <c r="O22" s="66"/>
-      <c r="P22" s="66"/>
-      <c r="Q22" s="66"/>
-      <c r="R22" s="66"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="67"/>
-      <c r="U22" s="68"/>
-      <c r="V22" s="68"/>
-      <c r="W22" s="68"/>
-      <c r="X22" s="68"/>
-      <c r="Y22" s="68"/>
-      <c r="Z22" s="68"/>
+      <c r="A22" s="62"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="64"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="64"/>
+      <c r="K22" s="64"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="65"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="65"/>
+      <c r="P22" s="65"/>
+      <c r="Q22" s="65"/>
+      <c r="R22" s="65"/>
+      <c r="S22" s="65"/>
+      <c r="T22" s="66"/>
+      <c r="U22" s="67"/>
+      <c r="V22" s="67"/>
+      <c r="W22" s="67"/>
+      <c r="X22" s="67"/>
+      <c r="Y22" s="67"/>
+      <c r="Z22" s="67"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="63"/>
-      <c r="B23" s="63"/>
-      <c r="C23" s="64"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="65"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="66"/>
-      <c r="M23" s="66"/>
-      <c r="N23" s="66"/>
-      <c r="O23" s="66"/>
-      <c r="P23" s="66"/>
-      <c r="Q23" s="66"/>
-      <c r="R23" s="66"/>
-      <c r="S23" s="66"/>
-      <c r="T23" s="67"/>
-      <c r="U23" s="68"/>
-      <c r="V23" s="68"/>
-      <c r="W23" s="68"/>
-      <c r="X23" s="68"/>
-      <c r="Y23" s="68"/>
-      <c r="Z23" s="68"/>
+      <c r="A23" s="62"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="63"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="64"/>
+      <c r="J23" s="64"/>
+      <c r="K23" s="64"/>
+      <c r="L23" s="65"/>
+      <c r="M23" s="65"/>
+      <c r="N23" s="65"/>
+      <c r="O23" s="65"/>
+      <c r="P23" s="65"/>
+      <c r="Q23" s="65"/>
+      <c r="R23" s="65"/>
+      <c r="S23" s="65"/>
+      <c r="T23" s="66"/>
+      <c r="U23" s="67"/>
+      <c r="V23" s="67"/>
+      <c r="W23" s="67"/>
+      <c r="X23" s="67"/>
+      <c r="Y23" s="67"/>
+      <c r="Z23" s="67"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="63"/>
-      <c r="B24" s="63"/>
-      <c r="C24" s="64"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64"/>
-      <c r="F24" s="64"/>
-      <c r="G24" s="65"/>
-      <c r="H24" s="65"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="65"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="66"/>
-      <c r="M24" s="66"/>
-      <c r="N24" s="66"/>
-      <c r="O24" s="66"/>
-      <c r="P24" s="66"/>
-      <c r="Q24" s="66"/>
-      <c r="R24" s="66"/>
-      <c r="S24" s="66"/>
-      <c r="T24" s="67"/>
-      <c r="U24" s="68"/>
-      <c r="V24" s="68"/>
-      <c r="W24" s="68"/>
-      <c r="X24" s="68"/>
-      <c r="Y24" s="68"/>
-      <c r="Z24" s="68"/>
+      <c r="A24" s="62"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="63"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="64"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="64"/>
+      <c r="K24" s="64"/>
+      <c r="L24" s="65"/>
+      <c r="M24" s="65"/>
+      <c r="N24" s="65"/>
+      <c r="O24" s="65"/>
+      <c r="P24" s="65"/>
+      <c r="Q24" s="65"/>
+      <c r="R24" s="65"/>
+      <c r="S24" s="65"/>
+      <c r="T24" s="66"/>
+      <c r="U24" s="67"/>
+      <c r="V24" s="67"/>
+      <c r="W24" s="67"/>
+      <c r="X24" s="67"/>
+      <c r="Y24" s="67"/>
+      <c r="Z24" s="67"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="63"/>
-      <c r="B25" s="63"/>
-      <c r="C25" s="64"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
-      <c r="F25" s="64"/>
-      <c r="G25" s="65"/>
-      <c r="H25" s="65"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="65"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="66"/>
-      <c r="M25" s="66"/>
-      <c r="N25" s="66"/>
-      <c r="O25" s="66"/>
-      <c r="P25" s="66"/>
-      <c r="Q25" s="66"/>
-      <c r="R25" s="66"/>
-      <c r="S25" s="66"/>
-      <c r="T25" s="67"/>
-      <c r="U25" s="68"/>
-      <c r="V25" s="68"/>
-      <c r="W25" s="68"/>
-      <c r="X25" s="68"/>
-      <c r="Y25" s="68"/>
-      <c r="Z25" s="68"/>
+      <c r="A25" s="62"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="63"/>
+      <c r="D25" s="63"/>
+      <c r="E25" s="63"/>
+      <c r="F25" s="63"/>
+      <c r="G25" s="64"/>
+      <c r="H25" s="64"/>
+      <c r="I25" s="64"/>
+      <c r="J25" s="64"/>
+      <c r="K25" s="64"/>
+      <c r="L25" s="65"/>
+      <c r="M25" s="65"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="65"/>
+      <c r="P25" s="65"/>
+      <c r="Q25" s="65"/>
+      <c r="R25" s="65"/>
+      <c r="S25" s="65"/>
+      <c r="T25" s="66"/>
+      <c r="U25" s="67"/>
+      <c r="V25" s="67"/>
+      <c r="W25" s="67"/>
+      <c r="X25" s="67"/>
+      <c r="Y25" s="67"/>
+      <c r="Z25" s="67"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="63"/>
-      <c r="B26" s="63"/>
-      <c r="C26" s="64"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="64"/>
-      <c r="F26" s="64"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="65"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="65"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="66"/>
-      <c r="M26" s="66"/>
-      <c r="N26" s="66"/>
-      <c r="O26" s="66"/>
-      <c r="P26" s="66"/>
-      <c r="Q26" s="66"/>
-      <c r="R26" s="66"/>
-      <c r="S26" s="66"/>
-      <c r="T26" s="67"/>
-      <c r="U26" s="68"/>
-      <c r="V26" s="68"/>
-      <c r="W26" s="68"/>
-      <c r="X26" s="68"/>
-      <c r="Y26" s="68"/>
-      <c r="Z26" s="68"/>
+      <c r="A26" s="62"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="64"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="64"/>
+      <c r="K26" s="64"/>
+      <c r="L26" s="65"/>
+      <c r="M26" s="65"/>
+      <c r="N26" s="65"/>
+      <c r="O26" s="65"/>
+      <c r="P26" s="65"/>
+      <c r="Q26" s="65"/>
+      <c r="R26" s="65"/>
+      <c r="S26" s="65"/>
+      <c r="T26" s="66"/>
+      <c r="U26" s="67"/>
+      <c r="V26" s="67"/>
+      <c r="W26" s="67"/>
+      <c r="X26" s="67"/>
+      <c r="Y26" s="67"/>
+      <c r="Z26" s="67"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="63"/>
-      <c r="B27" s="63"/>
-      <c r="C27" s="64"/>
-      <c r="D27" s="64"/>
-      <c r="E27" s="64"/>
-      <c r="F27" s="64"/>
-      <c r="G27" s="65"/>
-      <c r="H27" s="65"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="65"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="66"/>
-      <c r="M27" s="66"/>
-      <c r="N27" s="66"/>
-      <c r="O27" s="66"/>
-      <c r="P27" s="66"/>
-      <c r="Q27" s="66"/>
-      <c r="R27" s="66"/>
-      <c r="S27" s="66"/>
-      <c r="T27" s="67"/>
-      <c r="U27" s="68"/>
-      <c r="V27" s="68"/>
-      <c r="W27" s="68"/>
-      <c r="X27" s="68"/>
-      <c r="Y27" s="68"/>
-      <c r="Z27" s="68"/>
+      <c r="A27" s="62"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="63"/>
+      <c r="D27" s="63"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="64"/>
+      <c r="J27" s="64"/>
+      <c r="K27" s="64"/>
+      <c r="L27" s="65"/>
+      <c r="M27" s="65"/>
+      <c r="N27" s="65"/>
+      <c r="O27" s="65"/>
+      <c r="P27" s="65"/>
+      <c r="Q27" s="65"/>
+      <c r="R27" s="65"/>
+      <c r="S27" s="65"/>
+      <c r="T27" s="66"/>
+      <c r="U27" s="67"/>
+      <c r="V27" s="67"/>
+      <c r="W27" s="67"/>
+      <c r="X27" s="67"/>
+      <c r="Y27" s="67"/>
+      <c r="Z27" s="67"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="63"/>
-      <c r="B28" s="63"/>
-      <c r="C28" s="64"/>
-      <c r="D28" s="64"/>
-      <c r="E28" s="64"/>
-      <c r="F28" s="64"/>
-      <c r="G28" s="65"/>
-      <c r="H28" s="65"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="65"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="66"/>
-      <c r="M28" s="66"/>
-      <c r="N28" s="66"/>
-      <c r="O28" s="66"/>
-      <c r="P28" s="66"/>
-      <c r="Q28" s="66"/>
-      <c r="R28" s="66"/>
-      <c r="S28" s="66"/>
-      <c r="T28" s="67"/>
-      <c r="U28" s="68"/>
-      <c r="V28" s="68"/>
-      <c r="W28" s="68"/>
-      <c r="X28" s="68"/>
-      <c r="Y28" s="68"/>
-      <c r="Z28" s="68"/>
+      <c r="A28" s="62"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="63"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="64"/>
+      <c r="K28" s="64"/>
+      <c r="L28" s="65"/>
+      <c r="M28" s="65"/>
+      <c r="N28" s="65"/>
+      <c r="O28" s="65"/>
+      <c r="P28" s="65"/>
+      <c r="Q28" s="65"/>
+      <c r="R28" s="65"/>
+      <c r="S28" s="65"/>
+      <c r="T28" s="66"/>
+      <c r="U28" s="67"/>
+      <c r="V28" s="67"/>
+      <c r="W28" s="67"/>
+      <c r="X28" s="67"/>
+      <c r="Y28" s="67"/>
+      <c r="Z28" s="67"/>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="63"/>
-      <c r="B29" s="63"/>
-      <c r="C29" s="64"/>
-      <c r="D29" s="64"/>
-      <c r="E29" s="64"/>
-      <c r="F29" s="64"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="66"/>
-      <c r="M29" s="66"/>
-      <c r="N29" s="66"/>
-      <c r="O29" s="66"/>
-      <c r="P29" s="66"/>
-      <c r="Q29" s="66"/>
-      <c r="R29" s="66"/>
-      <c r="S29" s="66"/>
-      <c r="T29" s="67"/>
-      <c r="U29" s="68"/>
-      <c r="V29" s="68"/>
-      <c r="W29" s="68"/>
-      <c r="X29" s="68"/>
-      <c r="Y29" s="68"/>
-      <c r="Z29" s="68"/>
+      <c r="A29" s="62"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="63"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="63"/>
+      <c r="F29" s="63"/>
+      <c r="G29" s="64"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="64"/>
+      <c r="J29" s="64"/>
+      <c r="K29" s="64"/>
+      <c r="L29" s="65"/>
+      <c r="M29" s="65"/>
+      <c r="N29" s="65"/>
+      <c r="O29" s="65"/>
+      <c r="P29" s="65"/>
+      <c r="Q29" s="65"/>
+      <c r="R29" s="65"/>
+      <c r="S29" s="65"/>
+      <c r="T29" s="66"/>
+      <c r="U29" s="67"/>
+      <c r="V29" s="67"/>
+      <c r="W29" s="67"/>
+      <c r="X29" s="67"/>
+      <c r="Y29" s="67"/>
+      <c r="Z29" s="67"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="63"/>
-      <c r="B30" s="63"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="65"/>
-      <c r="H30" s="65"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="65"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="66"/>
-      <c r="M30" s="66"/>
-      <c r="N30" s="66"/>
-      <c r="O30" s="66"/>
-      <c r="P30" s="66"/>
-      <c r="Q30" s="66"/>
-      <c r="R30" s="66"/>
-      <c r="S30" s="66"/>
-      <c r="T30" s="67"/>
-      <c r="U30" s="68"/>
-      <c r="V30" s="68"/>
-      <c r="W30" s="68"/>
-      <c r="X30" s="68"/>
-      <c r="Y30" s="68"/>
-      <c r="Z30" s="68"/>
+      <c r="A30" s="62"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="63"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="63"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="64"/>
+      <c r="H30" s="64"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="64"/>
+      <c r="K30" s="64"/>
+      <c r="L30" s="65"/>
+      <c r="M30" s="65"/>
+      <c r="N30" s="65"/>
+      <c r="O30" s="65"/>
+      <c r="P30" s="65"/>
+      <c r="Q30" s="65"/>
+      <c r="R30" s="65"/>
+      <c r="S30" s="65"/>
+      <c r="T30" s="66"/>
+      <c r="U30" s="67"/>
+      <c r="V30" s="67"/>
+      <c r="W30" s="67"/>
+      <c r="X30" s="67"/>
+      <c r="Y30" s="67"/>
+      <c r="Z30" s="67"/>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="69"/>
-      <c r="B31" s="69"/>
-      <c r="C31" s="70"/>
-      <c r="D31" s="70"/>
-      <c r="E31" s="70"/>
-      <c r="F31" s="70"/>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="71"/>
-      <c r="J31" s="71"/>
-      <c r="K31" s="71"/>
-      <c r="L31" s="72"/>
-      <c r="M31" s="72"/>
-      <c r="N31" s="72"/>
-      <c r="O31" s="72"/>
-      <c r="P31" s="72"/>
-      <c r="Q31" s="72"/>
-      <c r="R31" s="72"/>
-      <c r="S31" s="72"/>
-      <c r="T31" s="73"/>
-      <c r="U31" s="68"/>
-      <c r="V31" s="68"/>
-      <c r="W31" s="68"/>
-      <c r="X31" s="68"/>
-      <c r="Y31" s="68"/>
-      <c r="Z31" s="68"/>
+      <c r="A31" s="68"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="69"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="70"/>
+      <c r="K31" s="70"/>
+      <c r="L31" s="71"/>
+      <c r="M31" s="71"/>
+      <c r="N31" s="71"/>
+      <c r="O31" s="71"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="71"/>
+      <c r="S31" s="71"/>
+      <c r="T31" s="72"/>
+      <c r="U31" s="67"/>
+      <c r="V31" s="67"/>
+      <c r="W31" s="67"/>
+      <c r="X31" s="67"/>
+      <c r="Y31" s="67"/>
+      <c r="Z31" s="67"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D32" s="7"/>

--- a/詳細設計図/タスク登録機能_詳細設計図.xlsx
+++ b/詳細設計図/タスク登録機能_詳細設計図.xlsx
@@ -5,15 +5,15 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="画面遷移図" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="ユースケース記述" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="詳細クラス図" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="画面設計書" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="テスト仕様書兼結果報告書" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="ユースケース記述" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="詳細クラス図" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="画面設計書_タスク登録画面" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="画面設計書_タスク登録完了画面" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="画面設計書_タスク登録エラー画面" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,12 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="95">
   <si>
     <t xml:space="preserve">プロジェクト型演習　成果ドキュメント</t>
   </si>
   <si>
-    <t xml:space="preserve">○○○○システム</t>
+    <t xml:space="preserve">タスク管理システム</t>
   </si>
   <si>
     <t xml:space="preserve">初版</t>
@@ -39,10 +39,10 @@
     <t xml:space="preserve">YYYY/MM/DD</t>
   </si>
   <si>
-    <t xml:space="preserve">チーム名</t>
-  </si>
-  <si>
-    <t xml:space="preserve">画面遷移図</t>
+    <t xml:space="preserve">MyTaskSystem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ユースケース記述</t>
   </si>
   <si>
     <t xml:space="preserve">システム名</t>
@@ -58,12 +58,6 @@
   </si>
   <si>
     <t xml:space="preserve">承認印</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ユースケース記述</t>
-  </si>
-  <si>
-    <t xml:space="preserve">タスク管理システム</t>
   </si>
   <si>
     <t xml:space="preserve">タスク登録機能</t>
@@ -187,6 +181,9 @@
     <t xml:space="preserve">action</t>
   </si>
   <si>
+    <t xml:space="preserve">Task-add-servlet</t>
+  </si>
+  <si>
     <t xml:space="preserve">method</t>
   </si>
   <si>
@@ -208,119 +205,161 @@
     <t xml:space="preserve">value</t>
   </si>
   <si>
-    <t xml:space="preserve">テスト仕様書兼
-結果報告書</t>
-  </si>
-  <si>
-    <t xml:space="preserve">テストレベル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">システムテスト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">テストベース</t>
-  </si>
-  <si>
-    <t xml:space="preserve">テスト対象</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ログイン画面</t>
-  </si>
-  <si>
-    <t xml:space="preserve">重要度</t>
-  </si>
-  <si>
-    <t xml:space="preserve">重要度は、次のいずれかを持つ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">◎：仕様　⇒100%解決する必要がある</t>
-  </si>
-  <si>
-    <t xml:space="preserve">○：重要　⇒別途テストパス率の指針に従う</t>
-  </si>
-  <si>
-    <t xml:space="preserve">△：重要ではない　⇒別途テストパス率の指針に従う</t>
-  </si>
-  <si>
-    <t xml:space="preserve">×：無くても良い　⇒個別に検討する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">系統</t>
-  </si>
-  <si>
-    <t xml:space="preserve">テストテーマ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">条件</t>
-  </si>
-  <si>
-    <t xml:space="preserve">操作手順</t>
-  </si>
-  <si>
-    <t xml:space="preserve">予測結果</t>
-  </si>
-  <si>
-    <t xml:space="preserve">テスト日</t>
-  </si>
-  <si>
-    <t xml:space="preserve">対応者</t>
-  </si>
-  <si>
-    <t xml:space="preserve">結果</t>
-  </si>
-  <si>
-    <t xml:space="preserve">◎</t>
-  </si>
-  <si>
-    <t xml:space="preserve">正常系
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URLアクセス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">なし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://localhost:8080/ans1101/login.html　へアクセスする</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ログイン画面へ遷移する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">○</t>
-  </si>
-  <si>
-    <t xml:space="preserve">異常系</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ユーザIDがDBに登録されていないときのログインボタン動作</t>
-  </si>
-  <si>
-    <t xml:space="preserve">・ユーザID：999999
-・パスワード：root</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ログインするボタンを押下する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エラー画面へ遷移する
-エラーの原因がユーザ名が未入力である旨通知する</t>
+    <t xml:space="preserve">①</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">タイトル画面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">②</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ユーザーにタスクの情報を入力させる誘導の文言</t>
+  </si>
+  <si>
+    <t xml:space="preserve">③</t>
+  </si>
+  <si>
+    <t xml:space="preserve">text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">taskName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">タスク名入力欄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">④</t>
+  </si>
+  <si>
+    <t xml:space="preserve">select</t>
+  </si>
+  <si>
+    <t xml:space="preserve">category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カテゴリID,カテゴリ名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カテゴリ情報がプルダウンで表示される。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⑤</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">timeLimit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">期限入力欄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⑥</t>
+  </si>
+  <si>
+    <t xml:space="preserve">user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ユーザID,ユーザ名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">担当者情報がプルダウンで表示される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⑦</t>
+  </si>
+  <si>
+    <t xml:space="preserve">status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ステータスコード,ステータス名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ステータス情報がプルダウンで表示される</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⑧</t>
+  </si>
+  <si>
+    <t xml:space="preserve">textarea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">memo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メモ入力欄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⑨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">submit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">登録</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フォームの情報を送信するボタン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⑩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">リセット</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入力した情報を取り消すボタン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">タスク登録完了画面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">menu.jsp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ユーザーにタスク情報の登録が成功したことを知らせる文言</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メニュー画面へ戻る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メニュー画面へ遷移するボタン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">タスク登録エラー画面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">task-add.jsp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ユーザーにタスク情報の登録が失敗したことを知らせる文言</t>
+  </si>
+  <si>
+    <t xml:space="preserve">登録画面に戻る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">登録画面へ遷移するボタン</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m\月d\日"/>
-    <numFmt numFmtId="166" formatCode="[$-411]h:mm"/>
+    <numFmt numFmtId="166" formatCode="m\月d\日"/>
+    <numFmt numFmtId="167" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -377,13 +416,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="MS PGothic"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
@@ -391,7 +423,7 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
       <family val="0"/>
@@ -412,7 +444,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="18">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -450,13 +482,6 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
-      <right/>
-      <top style="medium"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
       <right style="medium"/>
       <top style="medium"/>
       <bottom style="thin"/>
@@ -474,48 +499,6 @@
       <right style="medium"/>
       <top style="thin"/>
       <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="medium"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right/>
-      <top/>
-      <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="medium"/>
-      <top/>
-      <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -547,6 +530,20 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="medium"/>
       <right style="thin"/>
       <top style="medium"/>
@@ -572,62 +569,6 @@
       <right style="medium"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="dotted"/>
-      <right/>
-      <top style="dotted"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top style="dotted"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="dotted"/>
-      <top style="dotted"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="dotted"/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="dotted"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="dotted"/>
-      <right/>
-      <top/>
-      <bottom style="dotted"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="dotted"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="dotted"/>
-      <top/>
-      <bottom style="dotted"/>
       <diagonal/>
     </border>
   </borders>
@@ -656,7 +597,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="45">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -685,16 +626,20 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -709,67 +654,31 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -777,55 +686,67 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -837,116 +758,24 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1026,15 +855,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>104760</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>85680</xdr:rowOff>
+      <xdr:colOff>180360</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>154080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1086840</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>61560</xdr:rowOff>
+      <xdr:colOff>1017720</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>159120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1047,8 +876,137 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="104760" y="1000080"/>
-          <a:ext cx="9133560" cy="5805360"/>
+          <a:off x="180360" y="1230480"/>
+          <a:ext cx="8988840" cy="5348520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>857880</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>26640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1874520</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>173880</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="画像 2" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1945800" y="1569600"/>
+          <a:ext cx="4548240" cy="1747440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>428400</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>47880</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1060920</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>2248560</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="画像 3" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1516320" y="1590840"/>
+          <a:ext cx="6081840" cy="3800880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3960</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>161280</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>889200</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>3255840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="画像 4" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1091880" y="1704240"/>
+          <a:ext cx="7511760" cy="4694760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1378,9 +1336,11 @@
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="I14" s="7" t="n">
+        <v>45707</v>
+      </c>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G15" s="6"/>
@@ -1390,19 +1350,19 @@
       <c r="K15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2423,23 +2383,23 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="10" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10" t="s">
+      <c r="E1" s="11"/>
+      <c r="F1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="10"/>
+      <c r="G1" s="11"/>
       <c r="H1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="11" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="12" t="s">
@@ -2447,1614 +2407,194 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="13"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="13" t="s">
+        <v>1</v>
+      </c>
       <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="F2" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="14"/>
+      <c r="H2" s="14" t="n">
+        <v>45705</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="14"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="15"/>
+    </row>
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="16" t="s">
+        <v>13</v>
+      </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
+      <c r="D5" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
       <c r="J5" s="17"/>
     </row>
-    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="17"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="17"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="17"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="17"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="17"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="17"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="17"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="17"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="17"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="17"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="17"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="17"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="17"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="17"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="17"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="17"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="17"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="17"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="17"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="17"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="17"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="17"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="17"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="17"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="17"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="17"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="17"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="15"/>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="17"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="18"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="20"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="215" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="218" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="223" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="224" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="225" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="226" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="227" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="228" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="229" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="230" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="231" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="239" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="264" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="295" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="318" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="332" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="335" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="337" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="347" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="357" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="373" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="378" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="407" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="420" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="451" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="464" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="480" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="500" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="503" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="504" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="505" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="506" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="507" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="508" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="509" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="510" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="511" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="512" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="513" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="514" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="520" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="521" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="523" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="524" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="525" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="526" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="528" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="529" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="530" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="531" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="533" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="534" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="536" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="537" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="539" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="540" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="542" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="543" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="545" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="546" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="547" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="549" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="550" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="551" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="558" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="560" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="561" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="562" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="598" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="599" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="600" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="607" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="608" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="609" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="610" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="611" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="612" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="613" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="614" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="615" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="616" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="617" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="618" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="619" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="620" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="621" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="622" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="623" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="624" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="625" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="626" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="627" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="628" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="629" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="630" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="631" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="632" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="633" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="634" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="635" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="636" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="637" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="638" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="639" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="640" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="641" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="642" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="643" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="644" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="645" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="646" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="647" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="648" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="649" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="650" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="651" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="652" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="653" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="654" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="655" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="656" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="657" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="658" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="659" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="660" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="661" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="662" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="663" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="664" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="665" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="666" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="667" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="668" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="669" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="670" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="671" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="672" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="673" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="674" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="675" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="676" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="677" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="678" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="679" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="680" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="681" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="682" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="683" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="684" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="685" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="686" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="687" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="688" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="689" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="690" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="691" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="692" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="693" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="694" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="695" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="696" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="697" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="698" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="699" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="700" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="701" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="702" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="703" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="704" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="705" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="706" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="707" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="708" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="709" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="710" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="711" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="712" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="713" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="714" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="715" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="716" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="717" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="718" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="719" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="720" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="721" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="722" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="723" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="724" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="725" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="726" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="727" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="728" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="729" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="730" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="731" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="732" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="733" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="734" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="735" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="736" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="737" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="738" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="739" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="740" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="741" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="742" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="743" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="744" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="745" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="746" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="747" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="748" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="749" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="750" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="751" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="752" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="753" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="754" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="755" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="756" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="757" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="758" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="759" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="760" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="761" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="762" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="763" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="764" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="765" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="766" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="767" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="768" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="769" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="770" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="771" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="772" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="773" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="774" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="775" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="776" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="777" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="778" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="779" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="780" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="781" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="782" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="783" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="784" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="785" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="786" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="787" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="788" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="789" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="790" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="791" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="792" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="793" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="794" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="795" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="796" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="797" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="798" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="799" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="800" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="801" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="802" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="803" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="804" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="805" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="806" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="807" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="808" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="809" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="810" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="811" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="812" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="813" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="814" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="815" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="816" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="817" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="818" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="819" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="820" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="821" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="822" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="823" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="824" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="825" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="826" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="827" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="828" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="829" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="830" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="831" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="832" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="833" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="834" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="835" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="836" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="837" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="838" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="839" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="840" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="841" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="842" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="843" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="844" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="845" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="846" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="847" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="848" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="849" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="850" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="851" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="852" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="853" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="854" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="855" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="856" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="857" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="858" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="859" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="860" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="861" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="862" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="863" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="864" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="865" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="866" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="867" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="868" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="869" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="870" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="871" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="872" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="873" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="874" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="875" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="876" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="877" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="878" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="879" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="880" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="881" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="882" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="883" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="884" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="885" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="886" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="887" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="888" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="889" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="890" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="891" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="892" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="893" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="894" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="895" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="896" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="897" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="898" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="899" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="900" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="901" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="902" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="903" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="904" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="905" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="906" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="907" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="908" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="909" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="910" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="911" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="912" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="913" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="914" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="915" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="916" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="917" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="918" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="919" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="920" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="921" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="922" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="923" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="924" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="925" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="926" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="927" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="928" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="929" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="930" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="931" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="932" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="933" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="934" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="935" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="936" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="937" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="938" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="939" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="940" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="941" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="942" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="943" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="944" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="945" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="946" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="947" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="948" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="949" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="950" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="951" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="952" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="953" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="954" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="955" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="956" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="957" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="958" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="959" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="960" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="961" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="962" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="963" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="964" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="965" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="966" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="967" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="968" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="969" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="970" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="971" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="972" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="973" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="974" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="975" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="976" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="977" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="978" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="979" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="980" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="981" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="982" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="983" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="984" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="985" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="986" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="987" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="988" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="989" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="990" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="991" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="992" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="993" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="994" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="995" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="996" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="997" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="998" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="999" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1000" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.708333333333333" right="0.708333333333333" top="0.747916666666667" bottom="0.747916666666667" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:J1000"/>
-  <sheetFormatPr defaultColWidth="13.1328125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="4.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="4" style="1" width="15.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="11" style="1" width="7.93"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="22" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="23" t="n">
-        <v>45705</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="14"/>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="14"/>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="14"/>
-    </row>
-    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="25" t="s">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-    </row>
-    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="s">
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+    </row>
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="27" t="s">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-    </row>
-    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="s">
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+    </row>
+    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="27" t="s">
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-    </row>
-    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="s">
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+    </row>
+    <row r="9" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="27" t="s">
+      <c r="B9" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
-    </row>
-    <row r="9" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="28" t="s">
+      <c r="C9" s="21"/>
+      <c r="D9" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+    </row>
+    <row r="10" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20"/>
+      <c r="B10" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="30" t="s">
+      <c r="C10" s="21"/>
+      <c r="D10" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-    </row>
-    <row r="10" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="28"/>
-      <c r="B10" s="29" t="s">
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+    </row>
+    <row r="11" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20"/>
+      <c r="B11" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="30" t="s">
+      <c r="C11" s="21"/>
+      <c r="D11" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-    </row>
-    <row r="11" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28"/>
-      <c r="B11" s="29" t="s">
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+    </row>
+    <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="30" t="s">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-    </row>
-    <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26" t="s">
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+    </row>
+    <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="31" t="s">
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-    </row>
-    <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5083,7 +3623,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -5098,532 +3638,532 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="10" t="s">
+      <c r="A1" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10" t="s">
+      <c r="E1" s="11"/>
+      <c r="F1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="10"/>
-      <c r="H1" s="11" t="s">
+      <c r="G1" s="11"/>
+      <c r="H1" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="28" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="13" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" s="13"/>
-      <c r="H2" s="23" t="n">
+      <c r="H2" s="14" t="n">
         <v>45706</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="14"/>
+        <v>12</v>
+      </c>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="34"/>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
+      <c r="A5" s="29"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="34"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
+      <c r="A6" s="29"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="34"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="34"/>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="34"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
+      <c r="A9" s="29"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="34"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="34"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
+      <c r="A11" s="29"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="34"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
+      <c r="A12" s="29"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="34"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="34"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="34"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
+      <c r="A15" s="29"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="34"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
+      <c r="A16" s="29"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="34"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
+      <c r="A17" s="29"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="34"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="34"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="34"/>
+      <c r="A19" s="29"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="34"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
+      <c r="A20" s="29"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="34"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
+      <c r="A21" s="29"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="34"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
+      <c r="A22" s="29"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="34"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="34"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="34"/>
-      <c r="B24" s="34"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="34"/>
-      <c r="J24" s="34"/>
+      <c r="A24" s="29"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="34"/>
-      <c r="B25" s="34"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="34"/>
-      <c r="J25" s="34"/>
+      <c r="A25" s="29"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="34"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="34"/>
+      <c r="A26" s="29"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="34"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="34"/>
+      <c r="A27" s="29"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="34"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
+      <c r="A28" s="29"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="34"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="34"/>
-      <c r="J29" s="34"/>
+      <c r="A29" s="29"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="34"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="34"/>
-      <c r="J30" s="34"/>
+      <c r="A30" s="29"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="34"/>
-      <c r="B31" s="34"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="34"/>
+      <c r="A31" s="29"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="34"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="34"/>
+      <c r="A32" s="29"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="34"/>
-      <c r="B33" s="34"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="34"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="34"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="34"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="34"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="34"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="34"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="34"/>
+      <c r="A36" s="29"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="34"/>
-      <c r="B37" s="34"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="34"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="34"/>
+      <c r="A37" s="29"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="34"/>
-      <c r="B38" s="34"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="34"/>
-      <c r="I38" s="34"/>
-      <c r="J38" s="34"/>
+      <c r="A38" s="29"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="29"/>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="34"/>
-      <c r="B39" s="34"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="34"/>
-      <c r="I39" s="34"/>
-      <c r="J39" s="34"/>
+      <c r="A39" s="29"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="34"/>
-      <c r="B40" s="34"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="34"/>
-      <c r="I40" s="34"/>
-      <c r="J40" s="34"/>
+      <c r="A40" s="29"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="34"/>
-      <c r="B41" s="34"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="34"/>
-      <c r="I41" s="34"/>
-      <c r="J41" s="34"/>
+      <c r="A41" s="29"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
+      <c r="I41" s="29"/>
+      <c r="J41" s="29"/>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="34"/>
-      <c r="B42" s="34"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="34"/>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="34"/>
+      <c r="A42" s="29"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="29"/>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J44" s="35"/>
+      <c r="J44" s="30"/>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -6604,7 +5144,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -6613,335 +5153,492 @@
   <sheetFormatPr defaultColWidth="13.1328125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="4.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="4" style="1" width="15.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="15.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="24.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="1" width="15.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="11" style="1" width="7.93"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="10" t="s">
+      <c r="A1" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10" t="s">
+      <c r="E1" s="11"/>
+      <c r="F1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="10"/>
-      <c r="H1" s="11" t="s">
+      <c r="G1" s="11"/>
+      <c r="H1" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="28" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
       <c r="D2" s="13" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" s="13"/>
-      <c r="H2" s="23" t="n">
+      <c r="H2" s="14" t="n">
         <v>45706</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="37"/>
+        <v>12</v>
+      </c>
+      <c r="J2" s="32"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="36"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
+      <c r="A3" s="31"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="37"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="32"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
+      <c r="A4" s="31"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="37"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="32"/>
     </row>
     <row r="5" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+    </row>
+    <row r="6" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="39" t="s">
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+    </row>
+    <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="36"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+    </row>
+    <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="36"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+    </row>
+    <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="36"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+    </row>
+    <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="36"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+    </row>
+    <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="36"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+    </row>
+    <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="36"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+    </row>
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="36"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-    </row>
-    <row r="6" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="40" t="s">
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-    </row>
-    <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="41"/>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-    </row>
-    <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="41"/>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
-    </row>
-    <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="41"/>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-    </row>
-    <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="41"/>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-    </row>
-    <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="41"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="41"/>
-    </row>
-    <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="41"/>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="41"/>
-    </row>
-    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="41"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
-    </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="40" t="s">
+      <c r="B15" s="37"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="42" t="s">
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="44" t="s">
+      <c r="J15" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="J15" s="45" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="37" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="42" t="s">
+      <c r="B16" s="37"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="44" t="s">
+      <c r="E16" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="44" t="s">
+      <c r="F16" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="44" t="s">
+      <c r="G16" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="G16" s="44" t="s">
+      <c r="H16" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="H16" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="47"/>
-      <c r="B17" s="47"/>
-      <c r="C17" s="47"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="27"/>
-      <c r="J18" s="27"/>
+      <c r="A18" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="47"/>
-      <c r="B19" s="47"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
+      <c r="A19" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="47"/>
-      <c r="B20" s="47"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
+      <c r="A20" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="27"/>
+      <c r="A21" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="47"/>
-      <c r="B22" s="47"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="27"/>
+      <c r="A22" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="48"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="48"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="A23" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+    </row>
+    <row r="24" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="42"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+    </row>
+    <row r="25" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+    </row>
+    <row r="26" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
+    </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7917,7 +6614,7 @@
     <row r="999" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1000" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="37">
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -7949,6 +6646,12 @@
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7957,932 +6660,352 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:Z1000"/>
+  <dimension ref="A1:J1048576"/>
   <sheetFormatPr defaultColWidth="13.1328125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="1" width="2.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="7" style="1" width="7.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="21" style="1" width="7.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="4.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="15.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="24.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="15.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="18.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="11" style="1" width="7.93"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="11"/>
+      <c r="H1" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="13"/>
+      <c r="H2" s="14" t="n">
+        <v>45706</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="32"/>
+    </row>
+    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="31"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="32"/>
+    </row>
+    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="31"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="32"/>
+    </row>
+    <row r="5" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+    </row>
+    <row r="6" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+    </row>
+    <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="36"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+    </row>
+    <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="36"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+    </row>
+    <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="36"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+    </row>
+    <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="36"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+    </row>
+    <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="36"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+    </row>
+    <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="36"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+    </row>
+    <row r="13" customFormat="false" ht="191.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="36"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="37"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="J15" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="R1" s="10"/>
-      <c r="S1" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="T1" s="22"/>
-    </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14"/>
-    </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="38" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="37"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="25" t="s">
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="25"/>
-      <c r="R5" s="25"/>
-      <c r="S5" s="25"/>
-      <c r="T5" s="25"/>
-    </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="42" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="27"/>
-      <c r="R6" s="27"/>
-      <c r="S6" s="27"/>
-      <c r="T6" s="27"/>
-    </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="42" t="s">
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+    </row>
+    <row r="19" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="27"/>
-      <c r="N7" s="27"/>
-      <c r="O7" s="27"/>
-      <c r="P7" s="27"/>
-      <c r="Q7" s="27"/>
-      <c r="R7" s="27"/>
-      <c r="S7" s="27"/>
-      <c r="T7" s="27"/>
-    </row>
-    <row r="8" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
-      <c r="S8" s="16"/>
-      <c r="T8" s="17"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="50"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="52" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" s="53"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="54"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="51"/>
-      <c r="N9" s="51"/>
-      <c r="O9" s="51"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="51"/>
-      <c r="R9" s="51"/>
-      <c r="S9" s="51"/>
-      <c r="T9" s="55"/>
-      <c r="U9" s="51"/>
-      <c r="V9" s="51"/>
-      <c r="W9" s="51"/>
-      <c r="X9" s="51"/>
-      <c r="Y9" s="51"/>
-      <c r="Z9" s="51"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="50"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="56"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" s="51"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
-      <c r="K10" s="57"/>
-      <c r="L10" s="51"/>
-      <c r="M10" s="51"/>
-      <c r="N10" s="51"/>
-      <c r="O10" s="51"/>
-      <c r="P10" s="51"/>
-      <c r="Q10" s="51"/>
-      <c r="R10" s="51"/>
-      <c r="S10" s="51"/>
-      <c r="T10" s="55"/>
-      <c r="U10" s="51"/>
-      <c r="V10" s="51"/>
-      <c r="W10" s="51"/>
-      <c r="X10" s="51"/>
-      <c r="Y10" s="51"/>
-      <c r="Z10" s="51"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="50"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="56"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" s="51"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="57"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="51"/>
-      <c r="N11" s="51"/>
-      <c r="O11" s="51"/>
-      <c r="P11" s="51"/>
-      <c r="Q11" s="51"/>
-      <c r="R11" s="51"/>
-      <c r="S11" s="51"/>
-      <c r="T11" s="55"/>
-      <c r="U11" s="51"/>
-      <c r="V11" s="51"/>
-      <c r="W11" s="51"/>
-      <c r="X11" s="51"/>
-      <c r="Y11" s="51"/>
-      <c r="Z11" s="51"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="50"/>
-      <c r="B12" s="51"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" s="51"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
-      <c r="K12" s="57"/>
-      <c r="L12" s="51"/>
-      <c r="M12" s="51"/>
-      <c r="N12" s="51"/>
-      <c r="O12" s="51"/>
-      <c r="P12" s="51"/>
-      <c r="Q12" s="51"/>
-      <c r="R12" s="51"/>
-      <c r="S12" s="51"/>
-      <c r="T12" s="55"/>
-      <c r="U12" s="51"/>
-      <c r="V12" s="51"/>
-      <c r="W12" s="51"/>
-      <c r="X12" s="51"/>
-      <c r="Y12" s="51"/>
-      <c r="Z12" s="51"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="50"/>
-      <c r="B13" s="51"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="59"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="59"/>
-      <c r="J13" s="59"/>
-      <c r="K13" s="60"/>
-      <c r="L13" s="51"/>
-      <c r="M13" s="51"/>
-      <c r="N13" s="51"/>
-      <c r="O13" s="51"/>
-      <c r="P13" s="51"/>
-      <c r="Q13" s="51"/>
-      <c r="R13" s="51"/>
-      <c r="S13" s="51"/>
-      <c r="T13" s="55"/>
-      <c r="U13" s="51"/>
-      <c r="V13" s="51"/>
-      <c r="W13" s="51"/>
-      <c r="X13" s="51"/>
-      <c r="Y13" s="51"/>
-      <c r="Z13" s="51"/>
-    </row>
-    <row r="14" customFormat="false" ht="8.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="17"/>
-    </row>
-    <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="42"/>
-      <c r="C15" s="61" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" s="61"/>
-      <c r="E15" s="44" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="44"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="K15" s="44"/>
-      <c r="L15" s="44" t="s">
-        <v>64</v>
-      </c>
-      <c r="M15" s="44"/>
-      <c r="N15" s="44"/>
-      <c r="O15" s="44" t="s">
-        <v>65</v>
-      </c>
-      <c r="P15" s="44"/>
-      <c r="Q15" s="44"/>
-      <c r="R15" s="44" t="s">
-        <v>66</v>
-      </c>
-      <c r="S15" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="T15" s="46" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="62" t="n">
-        <v>1</v>
-      </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="63" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="63"/>
-      <c r="G16" s="64" t="s">
-        <v>71</v>
-      </c>
-      <c r="H16" s="64"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="K16" s="64"/>
-      <c r="L16" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="M16" s="65"/>
-      <c r="N16" s="65"/>
-      <c r="O16" s="65" t="s">
-        <v>74</v>
-      </c>
-      <c r="P16" s="65"/>
-      <c r="Q16" s="65"/>
-      <c r="R16" s="65"/>
-      <c r="S16" s="65"/>
-      <c r="T16" s="66"/>
-      <c r="U16" s="67"/>
-      <c r="V16" s="67"/>
-      <c r="W16" s="67"/>
-      <c r="X16" s="67"/>
-      <c r="Y16" s="67"/>
-      <c r="Z16" s="67"/>
-    </row>
-    <row r="17" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="62" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="63" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63" t="s">
-        <v>76</v>
-      </c>
-      <c r="F17" s="63"/>
-      <c r="G17" s="64" t="s">
-        <v>77</v>
-      </c>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="64" t="s">
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="K17" s="64"/>
-      <c r="L17" s="65" t="s">
-        <v>79</v>
-      </c>
-      <c r="M17" s="65"/>
-      <c r="N17" s="65"/>
-      <c r="O17" s="65" t="s">
-        <v>80</v>
-      </c>
-      <c r="P17" s="65"/>
-      <c r="Q17" s="65"/>
-      <c r="R17" s="65"/>
-      <c r="S17" s="65"/>
-      <c r="T17" s="66"/>
-      <c r="U17" s="67"/>
-      <c r="V17" s="67"/>
-      <c r="W17" s="67"/>
-      <c r="X17" s="67"/>
-      <c r="Y17" s="67"/>
-      <c r="Z17" s="67"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="62"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="64"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="64"/>
-      <c r="K18" s="64"/>
-      <c r="L18" s="65"/>
-      <c r="M18" s="65"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="65"/>
-      <c r="P18" s="65"/>
-      <c r="Q18" s="65"/>
-      <c r="R18" s="65"/>
-      <c r="S18" s="65"/>
-      <c r="T18" s="66"/>
-      <c r="U18" s="67"/>
-      <c r="V18" s="67"/>
-      <c r="W18" s="67"/>
-      <c r="X18" s="67"/>
-      <c r="Y18" s="67"/>
-      <c r="Z18" s="67"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="62"/>
-      <c r="B19" s="62"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="64"/>
-      <c r="L19" s="65"/>
-      <c r="M19" s="65"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="65"/>
-      <c r="P19" s="65"/>
-      <c r="Q19" s="65"/>
-      <c r="R19" s="65"/>
-      <c r="S19" s="65"/>
-      <c r="T19" s="66"/>
-      <c r="U19" s="67"/>
-      <c r="V19" s="67"/>
-      <c r="W19" s="67"/>
-      <c r="X19" s="67"/>
-      <c r="Y19" s="67"/>
-      <c r="Z19" s="67"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="62"/>
-      <c r="B20" s="62"/>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="64"/>
-      <c r="K20" s="64"/>
-      <c r="L20" s="65"/>
-      <c r="M20" s="65"/>
-      <c r="N20" s="65"/>
-      <c r="O20" s="65"/>
-      <c r="P20" s="65"/>
-      <c r="Q20" s="65"/>
-      <c r="R20" s="65"/>
-      <c r="S20" s="65"/>
-      <c r="T20" s="66"/>
-      <c r="U20" s="67"/>
-      <c r="V20" s="67"/>
-      <c r="W20" s="67"/>
-      <c r="X20" s="67"/>
-      <c r="Y20" s="67"/>
-      <c r="Z20" s="67"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="62"/>
-      <c r="B21" s="62"/>
-      <c r="C21" s="63"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="63"/>
-      <c r="F21" s="63"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="65"/>
-      <c r="M21" s="65"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="65"/>
-      <c r="P21" s="65"/>
-      <c r="Q21" s="65"/>
-      <c r="R21" s="65"/>
-      <c r="S21" s="65"/>
-      <c r="T21" s="66"/>
-      <c r="U21" s="67"/>
-      <c r="V21" s="67"/>
-      <c r="W21" s="67"/>
-      <c r="X21" s="67"/>
-      <c r="Y21" s="67"/>
-      <c r="Z21" s="67"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="62"/>
-      <c r="B22" s="62"/>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="64"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="64"/>
-      <c r="K22" s="64"/>
-      <c r="L22" s="65"/>
-      <c r="M22" s="65"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="65"/>
-      <c r="P22" s="65"/>
-      <c r="Q22" s="65"/>
-      <c r="R22" s="65"/>
-      <c r="S22" s="65"/>
-      <c r="T22" s="66"/>
-      <c r="U22" s="67"/>
-      <c r="V22" s="67"/>
-      <c r="W22" s="67"/>
-      <c r="X22" s="67"/>
-      <c r="Y22" s="67"/>
-      <c r="Z22" s="67"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="62"/>
-      <c r="B23" s="62"/>
-      <c r="C23" s="63"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="64"/>
-      <c r="K23" s="64"/>
-      <c r="L23" s="65"/>
-      <c r="M23" s="65"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="65"/>
-      <c r="P23" s="65"/>
-      <c r="Q23" s="65"/>
-      <c r="R23" s="65"/>
-      <c r="S23" s="65"/>
-      <c r="T23" s="66"/>
-      <c r="U23" s="67"/>
-      <c r="V23" s="67"/>
-      <c r="W23" s="67"/>
-      <c r="X23" s="67"/>
-      <c r="Y23" s="67"/>
-      <c r="Z23" s="67"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="62"/>
-      <c r="B24" s="62"/>
-      <c r="C24" s="63"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="64"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="64"/>
-      <c r="K24" s="64"/>
-      <c r="L24" s="65"/>
-      <c r="M24" s="65"/>
-      <c r="N24" s="65"/>
-      <c r="O24" s="65"/>
-      <c r="P24" s="65"/>
-      <c r="Q24" s="65"/>
-      <c r="R24" s="65"/>
-      <c r="S24" s="65"/>
-      <c r="T24" s="66"/>
-      <c r="U24" s="67"/>
-      <c r="V24" s="67"/>
-      <c r="W24" s="67"/>
-      <c r="X24" s="67"/>
-      <c r="Y24" s="67"/>
-      <c r="Z24" s="67"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="62"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="63"/>
-      <c r="D25" s="63"/>
-      <c r="E25" s="63"/>
-      <c r="F25" s="63"/>
-      <c r="G25" s="64"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="64"/>
-      <c r="J25" s="64"/>
-      <c r="K25" s="64"/>
-      <c r="L25" s="65"/>
-      <c r="M25" s="65"/>
-      <c r="N25" s="65"/>
-      <c r="O25" s="65"/>
-      <c r="P25" s="65"/>
-      <c r="Q25" s="65"/>
-      <c r="R25" s="65"/>
-      <c r="S25" s="65"/>
-      <c r="T25" s="66"/>
-      <c r="U25" s="67"/>
-      <c r="V25" s="67"/>
-      <c r="W25" s="67"/>
-      <c r="X25" s="67"/>
-      <c r="Y25" s="67"/>
-      <c r="Z25" s="67"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="62"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="63"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
-      <c r="F26" s="63"/>
-      <c r="G26" s="64"/>
-      <c r="H26" s="64"/>
-      <c r="I26" s="64"/>
-      <c r="J26" s="64"/>
-      <c r="K26" s="64"/>
-      <c r="L26" s="65"/>
-      <c r="M26" s="65"/>
-      <c r="N26" s="65"/>
-      <c r="O26" s="65"/>
-      <c r="P26" s="65"/>
-      <c r="Q26" s="65"/>
-      <c r="R26" s="65"/>
-      <c r="S26" s="65"/>
-      <c r="T26" s="66"/>
-      <c r="U26" s="67"/>
-      <c r="V26" s="67"/>
-      <c r="W26" s="67"/>
-      <c r="X26" s="67"/>
-      <c r="Y26" s="67"/>
-      <c r="Z26" s="67"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="62"/>
-      <c r="B27" s="62"/>
-      <c r="C27" s="63"/>
-      <c r="D27" s="63"/>
-      <c r="E27" s="63"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="64"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="64"/>
-      <c r="J27" s="64"/>
-      <c r="K27" s="64"/>
-      <c r="L27" s="65"/>
-      <c r="M27" s="65"/>
-      <c r="N27" s="65"/>
-      <c r="O27" s="65"/>
-      <c r="P27" s="65"/>
-      <c r="Q27" s="65"/>
-      <c r="R27" s="65"/>
-      <c r="S27" s="65"/>
-      <c r="T27" s="66"/>
-      <c r="U27" s="67"/>
-      <c r="V27" s="67"/>
-      <c r="W27" s="67"/>
-      <c r="X27" s="67"/>
-      <c r="Y27" s="67"/>
-      <c r="Z27" s="67"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="62"/>
-      <c r="B28" s="62"/>
-      <c r="C28" s="63"/>
-      <c r="D28" s="63"/>
-      <c r="E28" s="63"/>
-      <c r="F28" s="63"/>
-      <c r="G28" s="64"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="64"/>
-      <c r="J28" s="64"/>
-      <c r="K28" s="64"/>
-      <c r="L28" s="65"/>
-      <c r="M28" s="65"/>
-      <c r="N28" s="65"/>
-      <c r="O28" s="65"/>
-      <c r="P28" s="65"/>
-      <c r="Q28" s="65"/>
-      <c r="R28" s="65"/>
-      <c r="S28" s="65"/>
-      <c r="T28" s="66"/>
-      <c r="U28" s="67"/>
-      <c r="V28" s="67"/>
-      <c r="W28" s="67"/>
-      <c r="X28" s="67"/>
-      <c r="Y28" s="67"/>
-      <c r="Z28" s="67"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="62"/>
-      <c r="B29" s="62"/>
-      <c r="C29" s="63"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="63"/>
-      <c r="F29" s="63"/>
-      <c r="G29" s="64"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="64"/>
-      <c r="J29" s="64"/>
-      <c r="K29" s="64"/>
-      <c r="L29" s="65"/>
-      <c r="M29" s="65"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="65"/>
-      <c r="P29" s="65"/>
-      <c r="Q29" s="65"/>
-      <c r="R29" s="65"/>
-      <c r="S29" s="65"/>
-      <c r="T29" s="66"/>
-      <c r="U29" s="67"/>
-      <c r="V29" s="67"/>
-      <c r="W29" s="67"/>
-      <c r="X29" s="67"/>
-      <c r="Y29" s="67"/>
-      <c r="Z29" s="67"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="62"/>
-      <c r="B30" s="62"/>
-      <c r="C30" s="63"/>
-      <c r="D30" s="63"/>
-      <c r="E30" s="63"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="64"/>
-      <c r="K30" s="64"/>
-      <c r="L30" s="65"/>
-      <c r="M30" s="65"/>
-      <c r="N30" s="65"/>
-      <c r="O30" s="65"/>
-      <c r="P30" s="65"/>
-      <c r="Q30" s="65"/>
-      <c r="R30" s="65"/>
-      <c r="S30" s="65"/>
-      <c r="T30" s="66"/>
-      <c r="U30" s="67"/>
-      <c r="V30" s="67"/>
-      <c r="W30" s="67"/>
-      <c r="X30" s="67"/>
-      <c r="Y30" s="67"/>
-      <c r="Z30" s="67"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="68"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="69"/>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="70"/>
-      <c r="J31" s="70"/>
-      <c r="K31" s="70"/>
-      <c r="L31" s="71"/>
-      <c r="M31" s="71"/>
-      <c r="N31" s="71"/>
-      <c r="O31" s="71"/>
-      <c r="P31" s="71"/>
-      <c r="Q31" s="71"/>
-      <c r="R31" s="71"/>
-      <c r="S31" s="71"/>
-      <c r="T31" s="72"/>
-      <c r="U31" s="67"/>
-      <c r="V31" s="67"/>
-      <c r="W31" s="67"/>
-      <c r="X31" s="67"/>
-      <c r="Y31" s="67"/>
-      <c r="Z31" s="67"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
-    </row>
+      <c r="F19" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="H19" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -9843,151 +7966,38 @@
     <row r="991" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="992" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="993" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="994" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="995" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="996" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="997" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="998" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="999" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1000" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="136">
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="O31:Q31"/>
+  <mergeCells count="23">
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9996,5 +8006,1352 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:J1048576"/>
+  <sheetFormatPr defaultColWidth="13.1328125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="4.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="15.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="24.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="15.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="11" style="1" width="7.93"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="11"/>
+      <c r="H1" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="13"/>
+      <c r="H2" s="14" t="n">
+        <v>45706</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="32"/>
+    </row>
+    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="31"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="32"/>
+    </row>
+    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="31"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="32"/>
+    </row>
+    <row r="5" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+    </row>
+    <row r="6" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+    </row>
+    <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="36"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+    </row>
+    <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="36"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+    </row>
+    <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="36"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+    </row>
+    <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="36"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+    </row>
+    <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="36"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+    </row>
+    <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="36"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+    </row>
+    <row r="13" customFormat="false" ht="261.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="36"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="37"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="J15" s="40" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="37"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+    </row>
+    <row r="19" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="H19" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="215" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="218" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="223" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="224" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="225" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="226" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="227" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="228" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="229" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="230" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="231" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="239" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="264" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="295" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="318" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="332" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="335" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="337" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="347" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="357" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="373" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="378" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="407" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="420" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="451" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="464" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="480" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="500" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="503" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="504" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="505" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="506" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="507" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="508" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="509" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="510" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="511" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="512" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="513" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="514" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="520" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="521" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="523" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="524" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="525" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="526" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="528" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="529" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="530" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="531" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="533" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="534" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="536" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="537" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="539" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="540" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="542" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="543" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="545" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="546" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="547" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="549" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="550" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="551" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="558" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="560" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="561" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="562" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="598" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="599" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="600" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="607" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="608" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="609" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="610" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="611" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="612" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="613" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="614" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="615" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="616" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="617" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="618" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="619" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="620" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="621" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="622" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="623" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="624" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="625" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="626" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="627" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="628" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="629" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="630" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="631" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="632" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="633" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="634" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="635" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="636" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="637" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="638" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="639" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="640" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="641" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="642" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="643" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="644" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="645" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="646" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="647" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="648" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="649" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="650" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="651" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="652" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="653" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="654" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="655" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="656" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="657" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="658" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="659" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="660" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="661" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="662" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="663" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="664" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="665" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="666" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="667" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="668" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="669" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="670" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="671" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="672" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="673" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="674" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="675" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="676" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="677" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="678" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="679" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="680" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="681" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="682" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="683" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="684" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="685" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="686" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="687" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="688" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="689" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="690" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="691" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="692" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="693" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="694" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="695" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="696" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="697" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="698" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="699" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="700" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="701" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="702" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="703" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="704" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="705" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="706" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="707" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="708" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="709" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="710" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="711" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="712" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="713" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="714" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="715" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="716" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="717" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="718" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="719" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="720" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="721" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="722" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="723" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="724" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="725" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="726" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="727" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="728" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="729" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="730" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="731" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="732" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="733" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="734" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="735" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="736" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="737" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="738" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="739" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="740" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="741" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="742" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="743" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="744" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="745" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="746" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="747" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="748" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="749" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="750" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="751" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="752" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="753" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="754" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="755" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="756" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="757" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="758" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="759" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="760" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="761" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="762" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="763" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="764" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="765" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="766" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="767" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="768" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="769" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="770" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="771" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="772" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="773" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="774" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="775" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="776" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="777" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="778" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="779" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="780" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="781" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="782" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="783" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="784" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="785" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="786" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="787" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="788" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="789" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="790" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="791" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="792" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="793" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="794" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="795" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="796" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="797" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="798" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="799" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="800" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="801" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="802" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="803" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="804" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="805" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="806" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="807" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="808" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="809" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="810" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="811" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="812" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="813" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="814" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="815" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="816" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="817" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="818" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="819" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="820" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="821" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="822" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="823" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="824" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="825" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="826" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="827" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="828" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="829" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="830" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="831" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="832" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="833" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="834" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="835" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="836" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="837" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="838" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="839" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="840" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="841" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="842" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="843" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="844" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="845" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="846" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="847" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="848" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="849" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="850" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="851" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="852" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="853" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="854" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="855" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="856" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="857" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="858" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="859" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="860" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="861" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="862" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="863" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="864" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="865" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="866" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="867" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="868" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="869" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="870" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="871" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="872" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="873" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="874" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="875" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="876" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="877" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="878" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="879" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="880" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="881" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="882" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="883" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="884" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="885" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="886" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="887" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="888" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="889" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="890" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="891" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="892" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="893" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="894" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="895" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="896" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="897" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="898" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="899" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="900" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="901" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="902" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="903" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="904" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="905" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="906" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="907" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="908" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="909" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="910" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="911" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="912" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="913" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="914" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="915" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="916" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="917" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="918" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="919" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="920" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="921" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="922" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="923" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="924" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="925" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="926" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="927" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="928" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="929" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="930" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="931" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="932" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="933" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="934" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="935" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="936" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="937" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="938" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="939" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="940" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="941" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="942" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="943" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="944" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="945" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="946" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="947" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="948" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="949" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="950" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="951" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="952" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="953" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="954" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="955" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="956" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="957" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="958" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="959" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="960" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="961" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="962" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="963" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="964" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="965" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="966" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="967" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="968" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="969" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="970" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="971" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="972" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="973" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="974" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="975" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="976" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="977" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="978" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="979" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="980" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="981" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="982" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="983" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="984" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="985" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="986" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="987" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="988" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="989" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="990" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="991" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="992" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="993" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/詳細設計図/タスク登録機能_詳細設計図.xlsx
+++ b/詳細設計図/タスク登録機能_詳細設計図.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" state="visible" r:id="rId3"/>
@@ -353,11 +353,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m\月d\日"/>
-    <numFmt numFmtId="166" formatCode="m\月d\日"/>
-    <numFmt numFmtId="167" formatCode="[$-411]h:mm"/>
+    <numFmt numFmtId="166" formatCode="[$-411]h:mm"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -654,7 +653,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -718,7 +717,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -861,9 +860,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1017720</xdr:colOff>
+      <xdr:colOff>1017360</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>159120</xdr:rowOff>
+      <xdr:rowOff>158760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -877,7 +876,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="180360" y="1230480"/>
-          <a:ext cx="8988840" cy="5348520"/>
+          <a:ext cx="8988480" cy="5348160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -904,9 +903,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1874520</xdr:colOff>
+      <xdr:colOff>1874160</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>173880</xdr:rowOff>
+      <xdr:rowOff>173520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -920,7 +919,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1945800" y="1569600"/>
-          <a:ext cx="4548240" cy="1747440"/>
+          <a:ext cx="4547880" cy="1747080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -947,9 +946,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1060920</xdr:colOff>
+      <xdr:colOff>1060560</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>2248560</xdr:rowOff>
+      <xdr:rowOff>2248200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -963,7 +962,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1516320" y="1590840"/>
-          <a:ext cx="6081840" cy="3800880"/>
+          <a:ext cx="6081480" cy="3800520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -990,9 +989,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>889200</xdr:colOff>
+      <xdr:colOff>888840</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>3255840</xdr:rowOff>
+      <xdr:rowOff>3255480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1006,7 +1005,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1091880" y="1704240"/>
-          <a:ext cx="7511760" cy="4694760"/>
+          <a:ext cx="7511400" cy="4694400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2411,7 +2410,7 @@
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
       <c r="D2" s="13" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="13" t="s">
@@ -3666,7 +3665,7 @@
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
       <c r="D2" s="13" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="13" t="s">
@@ -5188,7 +5187,7 @@
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="13" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="13" t="s">
@@ -6709,7 +6708,7 @@
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="13" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="13" t="s">
@@ -8055,7 +8054,7 @@
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="13" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="13" t="s">

--- a/詳細設計図/タスク登録機能_詳細設計図.xlsx
+++ b/詳細設計図/タスク登録機能_詳細設計図.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" state="visible" r:id="rId3"/>
@@ -128,7 +128,8 @@
       </rPr>
       <t xml:space="preserve">③ユーザーは、「登録する」ボタンを押下する。
 ④ユーザーは、入力された情報をチェックする。(Alt-2)
-⑤システムは、入力された情報を登録する。</t>
+⑤システムは、入力された情報をテーブル（t-task）に登録する。
+⑥システムは、タスク登録完了画面に遷移する。</t>
     </r>
   </si>
   <si>
@@ -860,9 +861,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1017360</xdr:colOff>
+      <xdr:colOff>1017000</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>158760</xdr:rowOff>
+      <xdr:rowOff>158400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -876,7 +877,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="180360" y="1230480"/>
-          <a:ext cx="8988480" cy="5348160"/>
+          <a:ext cx="8988120" cy="5347800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -903,9 +904,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1874160</xdr:colOff>
+      <xdr:colOff>1873800</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>173520</xdr:rowOff>
+      <xdr:rowOff>173160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -919,7 +920,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1945800" y="1569600"/>
-          <a:ext cx="4547880" cy="1747080"/>
+          <a:ext cx="4547520" cy="1746720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -946,9 +947,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1060560</xdr:colOff>
+      <xdr:colOff>1060200</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>2248200</xdr:rowOff>
+      <xdr:rowOff>2247840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -962,7 +963,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1516320" y="1590840"/>
-          <a:ext cx="6081480" cy="3800520"/>
+          <a:ext cx="6081120" cy="3800160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -989,9 +990,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>888840</xdr:colOff>
+      <xdr:colOff>888480</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>3255480</xdr:rowOff>
+      <xdr:rowOff>3255120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1005,7 +1006,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1091880" y="1704240"/>
-          <a:ext cx="7511400" cy="4694400"/>
+          <a:ext cx="7511040" cy="4694040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/詳細設計図/タスク登録機能_詳細設計図.xlsx
+++ b/詳細設計図/タスク登録機能_詳細設計図.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" state="visible" r:id="rId3"/>
@@ -128,8 +128,7 @@
       </rPr>
       <t xml:space="preserve">③ユーザーは、「登録する」ボタンを押下する。
 ④ユーザーは、入力された情報をチェックする。(Alt-2)
-⑤システムは、入力された情報をテーブル（t-task）に登録する。
-⑥システムは、タスク登録完了画面に遷移する。</t>
+⑤システムは、入力された情報を登録する。</t>
     </r>
   </si>
   <si>
@@ -855,15 +854,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>180360</xdr:colOff>
+      <xdr:colOff>8280</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>154080</xdr:rowOff>
+      <xdr:rowOff>91440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1017000</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>158400</xdr:rowOff>
+      <xdr:colOff>1069560</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>141840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -876,8 +875,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="180360" y="1230480"/>
-          <a:ext cx="8988120" cy="5347800"/>
+          <a:off x="8280" y="1167840"/>
+          <a:ext cx="9212760" cy="5555880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -904,9 +903,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1873800</xdr:colOff>
+      <xdr:colOff>1873080</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>173160</xdr:rowOff>
+      <xdr:rowOff>172440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -920,7 +919,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1945800" y="1569600"/>
-          <a:ext cx="4547520" cy="1746720"/>
+          <a:ext cx="4546800" cy="1746000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -947,9 +946,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1060200</xdr:colOff>
+      <xdr:colOff>1059480</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>2247840</xdr:rowOff>
+      <xdr:rowOff>2247120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -963,7 +962,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1516320" y="1590840"/>
-          <a:ext cx="6081120" cy="3800160"/>
+          <a:ext cx="6080400" cy="3799440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -990,9 +989,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>888480</xdr:colOff>
+      <xdr:colOff>887760</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>3255120</xdr:rowOff>
+      <xdr:rowOff>3254400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1006,7 +1005,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1091880" y="1704240"/>
-          <a:ext cx="7511040" cy="4694040"/>
+          <a:ext cx="7510320" cy="4693320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/詳細設計図/タスク登録機能_詳細設計図.xlsx
+++ b/詳細設計図/タスク登録機能_詳細設計図.xlsx
@@ -181,7 +181,7 @@
     <t xml:space="preserve">action</t>
   </si>
   <si>
-    <t xml:space="preserve">Task-add-servlet</t>
+    <t xml:space="preserve">task-add-servlet</t>
   </si>
   <si>
     <t xml:space="preserve">method</t>
@@ -854,15 +854,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>8280</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:rowOff>16560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1069560</xdr:colOff>
+      <xdr:colOff>1107000</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>141840</xdr:rowOff>
+      <xdr:rowOff>84960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -875,8 +875,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8280" y="1167840"/>
-          <a:ext cx="9212760" cy="5555880"/>
+          <a:off x="0" y="1092960"/>
+          <a:ext cx="9258480" cy="5573880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -903,9 +903,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1873080</xdr:colOff>
+      <xdr:colOff>1872360</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>172440</xdr:rowOff>
+      <xdr:rowOff>171720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -919,7 +919,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1945800" y="1569600"/>
-          <a:ext cx="4546800" cy="1746000"/>
+          <a:ext cx="4546080" cy="1745280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -946,9 +946,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1059480</xdr:colOff>
+      <xdr:colOff>1058760</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>2247120</xdr:rowOff>
+      <xdr:rowOff>2246400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -962,7 +962,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1516320" y="1590840"/>
-          <a:ext cx="6080400" cy="3799440"/>
+          <a:ext cx="6079680" cy="3798720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -989,9 +989,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>887760</xdr:colOff>
+      <xdr:colOff>887040</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>3254400</xdr:rowOff>
+      <xdr:rowOff>3253680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1005,7 +1005,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1091880" y="1704240"/>
-          <a:ext cx="7510320" cy="4693320"/>
+          <a:ext cx="7509600" cy="4692600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/詳細設計図/タスク登録機能_詳細設計図.xlsx
+++ b/詳細設計図/タスク登録機能_詳細設計図.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" state="visible" r:id="rId3"/>
@@ -127,8 +127,9 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">③ユーザーは、「登録する」ボタンを押下する。
-④ユーザーは、入力された情報をチェックする。(Alt-2)
-⑤システムは、入力された情報を登録する。</t>
+④システムは、入力された情報をチェックする。(Alt-2)
+⑤システムは、入力された情報を登録する。
+⑥システムは、[タスク登録完了画面]に遷移する。</t>
     </r>
   </si>
   <si>
@@ -144,8 +145,28 @@
     <t xml:space="preserve">例外フロー</t>
   </si>
   <si>
-    <t xml:space="preserve">Alt-2：「期限」「メモ」以外にNULLが含まれていた場合
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS PGothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Alt-2：「期限」「メモ」以外にNULLが含まれていた場合、
+　　　　また、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS PGothic"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">「タスク名」「メモ」に最大文字数+1文字以上の文字が入力された場合（タスク名：51以上,メモ：101以上）
 1.エラー画面に遷移する</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">事後条件</t>
@@ -860,9 +881,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1107000</xdr:colOff>
+      <xdr:colOff>1105200</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>84960</xdr:rowOff>
+      <xdr:rowOff>83160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -876,7 +897,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="1092960"/>
-          <a:ext cx="9258480" cy="5573880"/>
+          <a:ext cx="9256680" cy="5572080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -903,9 +924,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1872360</xdr:colOff>
+      <xdr:colOff>1870560</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>171720</xdr:rowOff>
+      <xdr:rowOff>169920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -919,7 +940,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1945800" y="1569600"/>
-          <a:ext cx="4546080" cy="1745280"/>
+          <a:ext cx="4544280" cy="1743480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -946,9 +967,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1058760</xdr:colOff>
+      <xdr:colOff>1056960</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>2246400</xdr:rowOff>
+      <xdr:rowOff>2244600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -962,7 +983,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1516320" y="1590840"/>
-          <a:ext cx="6079680" cy="3798720"/>
+          <a:ext cx="6077880" cy="3796920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -989,9 +1010,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>887040</xdr:colOff>
+      <xdr:colOff>885240</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>3253680</xdr:rowOff>
+      <xdr:rowOff>3251880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1005,7 +1026,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1091880" y="1704240"/>
-          <a:ext cx="7509600" cy="4692600"/>
+          <a:ext cx="7507800" cy="4690800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2513,7 +2534,7 @@
       <c r="I8" s="19"/>
       <c r="J8" s="19"/>
     </row>
-    <row r="9" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="78.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="20" t="s">
         <v>21</v>
       </c>

--- a/詳細設計図/タスク登録機能_詳細設計図.xlsx
+++ b/詳細設計図/タスク登録機能_詳細設計図.xlsx
@@ -274,7 +274,7 @@
     <t xml:space="preserve">date</t>
   </si>
   <si>
-    <t xml:space="preserve">timeLimit</t>
+    <t xml:space="preserve">limitDate</t>
   </si>
   <si>
     <t xml:space="preserve">期限入力欄</t>
@@ -881,9 +881,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1105200</xdr:colOff>
+      <xdr:colOff>1104840</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>83160</xdr:rowOff>
+      <xdr:rowOff>82800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -897,7 +897,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="1092960"/>
-          <a:ext cx="9256680" cy="5572080"/>
+          <a:ext cx="9256320" cy="5571720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -924,9 +924,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1870560</xdr:colOff>
+      <xdr:colOff>1870200</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>169920</xdr:rowOff>
+      <xdr:rowOff>169560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -940,7 +940,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1945800" y="1569600"/>
-          <a:ext cx="4544280" cy="1743480"/>
+          <a:ext cx="4543920" cy="1743120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -967,9 +967,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1056960</xdr:colOff>
+      <xdr:colOff>1056600</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>2244600</xdr:rowOff>
+      <xdr:rowOff>2244240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -983,7 +983,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1516320" y="1590840"/>
-          <a:ext cx="6077880" cy="3796920"/>
+          <a:ext cx="6077520" cy="3796560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1010,9 +1010,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>885240</xdr:colOff>
+      <xdr:colOff>884880</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>3251880</xdr:rowOff>
+      <xdr:rowOff>3251520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1026,7 +1026,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1091880" y="1704240"/>
-          <a:ext cx="7507800" cy="4690800"/>
+          <a:ext cx="7507440" cy="4690440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
